--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -43012,23 +43012,23 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -43037,16 +43037,16 @@
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.5528</v>
@@ -43055,7 +43055,7 @@
         <v>1.0135</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -43120,14 +43120,14 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -43145,16 +43145,16 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.8333</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.5528</v>
@@ -43163,7 +43163,7 @@
         <v>1.0135</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="38">
@@ -43174,30 +43174,30 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
@@ -43208,7 +43208,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>1.5528</v>
@@ -43282,14 +43282,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -43316,7 +43316,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.3314</v>
@@ -43336,14 +43336,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -43352,14 +43352,14 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
         <v>1</v>
       </c>
@@ -43370,7 +43370,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.3314</v>
@@ -43390,41 +43390,41 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>L. PIERA FLO</t>
+          <t>A. STANACEV</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>0.8097</v>
@@ -43444,23 +43444,23 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A. STANACEV</t>
+          <t>L. PIERA FLO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -43472,13 +43472,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.8097</v>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>C. MELIA</t>
+          <t>K. GALICKOVA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -43887,7 +43887,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -43907,16 +43907,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>1.8041</v>
+        <v>1.8908</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.6803</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="N51" s="10" t="n">
         <v>0</v>
@@ -43930,7 +43930,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>K. GALICKOVA</t>
+          <t>C. MELIA</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -43941,19 +43941,19 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H52" s="8" t="n">
         <v>0</v>
       </c>
@@ -43961,16 +43961,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>1.8908</v>
+        <v>1.8041</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6803</v>
       </c>
       <c r="N52" s="10" t="n">
         <v>0</v>
@@ -43984,18 +43984,18 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -44005,7 +44005,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
@@ -44038,28 +44038,28 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
@@ -44092,18 +44092,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -44146,14 +44146,14 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -44200,14 +44200,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -43012,30 +43012,30 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
       </c>
@@ -43046,7 +43046,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.5528</v>
@@ -43066,18 +43066,18 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -43087,7 +43087,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
@@ -43100,7 +43100,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.5528</v>
@@ -43174,23 +43174,23 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -43208,7 +43208,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>1.5528</v>
@@ -43228,28 +43228,28 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -43262,7 +43262,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -43282,14 +43282,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -43298,14 +43298,14 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H40" s="8" t="n">
         <v>1</v>
       </c>
@@ -43316,7 +43316,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.3314</v>
@@ -43336,14 +43336,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -43370,7 +43370,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.3314</v>
@@ -43390,23 +43390,23 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>A. STANACEV</t>
+          <t>L. PIERA FLO</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -43418,13 +43418,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>0.8097</v>
@@ -43444,41 +43444,41 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>L. PIERA FLO</t>
+          <t>A. STANACEV</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.8097</v>
@@ -43984,28 +43984,28 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
@@ -44038,18 +44038,18 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -44059,7 +44059,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
@@ -44092,18 +44092,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -44200,14 +44200,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -44216,12 +44216,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -44254,14 +44254,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -44270,12 +44270,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -43012,23 +43012,23 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -43046,7 +43046,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.5528</v>
@@ -43066,30 +43066,30 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
@@ -43100,7 +43100,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.5528</v>
@@ -43120,14 +43120,14 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -43136,25 +43136,25 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.5528</v>
@@ -43163,7 +43163,7 @@
         <v>1.0135</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -43174,41 +43174,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>1.5528</v>
@@ -43217,7 +43217,7 @@
         <v>1.0135</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="39">
@@ -43228,18 +43228,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -43262,7 +43262,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -43282,14 +43282,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -43316,7 +43316,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.3314</v>
@@ -43336,14 +43336,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -43352,14 +43352,14 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
         <v>1</v>
       </c>
@@ -43370,7 +43370,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.3314</v>
@@ -43390,41 +43390,41 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>L. PIERA FLO</t>
+          <t>A. STANACEV</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>0.8097</v>
@@ -43444,23 +43444,23 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A. STANACEV</t>
+          <t>L. PIERA FLO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -43472,13 +43472,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.8097</v>
@@ -43984,18 +43984,18 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -44005,7 +44005,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
@@ -44038,28 +44038,28 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
@@ -44092,18 +44092,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -44200,14 +44200,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -44216,12 +44216,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -44254,14 +44254,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -44270,12 +44270,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -44578,7 +44578,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -44632,7 +44632,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -45118,7 +45118,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>N. PRIEDE</t>
+          <t>T. EKE BENITEZ</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -45172,7 +45172,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>T. EKE BENITEZ</t>
+          <t>N. PRIEDE</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -60861,18 +60861,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -60882,7 +60882,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -60895,7 +60895,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -60915,23 +60915,23 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -60949,7 +60949,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -61023,30 +61023,30 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
@@ -61057,7 +61057,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -61077,28 +61077,28 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
@@ -61111,7 +61111,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>1.5528</v>
@@ -61725,28 +61725,28 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61833,18 +61833,18 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -61887,14 +61887,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -61903,12 +61903,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -61941,14 +61941,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -61957,12 +61957,12 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -62751,14 +62751,14 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -62785,7 +62785,7 @@
         <v>5</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>2.5</v>
@@ -62805,7 +62805,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -62859,18 +62859,18 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -62893,7 +62893,7 @@
         <v>5</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>2.5</v>
@@ -62913,14 +62913,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -62929,7 +62929,7 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -62947,7 +62947,7 @@
         <v>5</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>2.5</v>
@@ -62967,18 +62967,18 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -63001,7 +63001,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
         <v>2.5</v>
@@ -63075,7 +63075,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -63086,7 +63086,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -63183,7 +63183,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -63237,7 +63237,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -63291,7 +63291,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -63302,7 +63302,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -60483,23 +60483,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -60517,7 +60517,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.484</v>
@@ -60537,23 +60537,23 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -60571,7 +60571,7 @@
         <v>5</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.484</v>
@@ -60861,7 +60861,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -60877,7 +60877,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -60915,41 +60915,41 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -60958,7 +60958,7 @@
         <v>1.0135</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="41">
@@ -60969,23 +60969,23 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -60994,16 +60994,16 @@
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -61012,7 +61012,7 @@
         <v>1.0135</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -61023,14 +61023,14 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -61039,12 +61039,12 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -61057,7 +61057,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -61077,14 +61077,14 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
@@ -61093,14 +61093,14 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
@@ -61111,7 +61111,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>1.5528</v>
@@ -61725,18 +61725,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -61746,7 +61746,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61833,28 +61833,28 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -61887,14 +61887,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -61903,12 +61903,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -61941,7 +61941,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -61957,7 +61957,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -61995,14 +61995,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -62265,7 +62265,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -62751,23 +62751,23 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -62785,7 +62785,7 @@
         <v>5</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>2.5</v>
@@ -62805,14 +62805,14 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -62839,7 +62839,7 @@
         <v>5</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2.5</v>
@@ -62859,18 +62859,18 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -62893,7 +62893,7 @@
         <v>5</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>2.5</v>
@@ -62913,7 +62913,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -62967,7 +62967,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -63075,7 +63075,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -63086,7 +63086,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -63129,7 +63129,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -63183,7 +63183,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -63194,7 +63194,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -63237,7 +63237,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -63291,7 +63291,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -2728,7 +2728,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
@@ -60483,23 +60483,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -60517,7 +60517,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.484</v>
@@ -60537,23 +60537,23 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -60571,7 +60571,7 @@
         <v>5</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.484</v>
@@ -60861,28 +60861,28 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -60895,7 +60895,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -60915,14 +60915,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -60940,16 +60940,16 @@
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.5</v>
+        <v>0.8333</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -60958,7 +60958,7 @@
         <v>1.0135</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -60969,41 +60969,41 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -61012,7 +61012,7 @@
         <v>1.0135</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="42">
@@ -61023,30 +61023,30 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
         <v>0</v>
       </c>
@@ -61057,7 +61057,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -61077,23 +61077,23 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -61111,7 +61111,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>1.5528</v>
@@ -61131,41 +61131,41 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>L. PIERA FLO</t>
+          <t>A. STANACEV</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>0.8097</v>
@@ -61185,23 +61185,23 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A. STANACEV</t>
+          <t>L. PIERA FLO</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -61213,13 +61213,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>0.8097</v>
@@ -61725,28 +61725,28 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61779,18 +61779,18 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -61800,7 +61800,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -61833,18 +61833,18 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -61887,7 +61887,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -61903,7 +61903,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -61941,7 +61941,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -61957,7 +61957,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -62265,7 +62265,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -62751,18 +62751,18 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -62785,7 +62785,7 @@
         <v>5</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>2.5</v>
@@ -62805,23 +62805,23 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -62839,7 +62839,7 @@
         <v>5</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2.5</v>
@@ -62859,14 +62859,14 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -62893,7 +62893,7 @@
         <v>5</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>2.5</v>
@@ -62967,7 +62967,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -63129,7 +63129,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -63183,7 +63183,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -63194,7 +63194,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -63237,7 +63237,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -63248,7 +63248,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -63291,7 +63291,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -60861,18 +60861,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -60882,7 +60882,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -60895,7 +60895,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -60915,23 +60915,23 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -60949,7 +60949,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -60969,14 +60969,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -60985,25 +60985,25 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -61012,7 +61012,7 @@
         <v>1.0135</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -61023,41 +61023,41 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -61066,7 +61066,7 @@
         <v>1.0135</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="43">
@@ -61077,30 +61077,30 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
@@ -61111,7 +61111,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>1.5528</v>
@@ -61725,18 +61725,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -61746,7 +61746,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61779,28 +61779,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -61833,18 +61833,18 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -61887,14 +61887,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -61908,7 +61908,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -61995,14 +61995,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -62265,7 +62265,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -62913,7 +62913,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -62967,7 +62967,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -63129,7 +63129,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -63183,7 +63183,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -63291,7 +63291,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -63345,7 +63345,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>T. EKE BENITEZ</t>
+          <t>N. PRIEDE</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -63399,7 +63399,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>N. PRIEDE</t>
+          <t>T. EKE BENITEZ</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -60483,23 +60483,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -60517,7 +60517,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.484</v>
@@ -60537,23 +60537,23 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -60571,7 +60571,7 @@
         <v>5</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.484</v>
@@ -60915,28 +60915,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
@@ -60949,7 +60949,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -60969,30 +60969,30 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
@@ -61003,7 +61003,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -61725,28 +61725,28 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61779,18 +61779,18 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -61800,7 +61800,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -61887,14 +61887,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -61903,12 +61903,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -61941,14 +61941,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -61957,12 +61957,12 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -62751,7 +62751,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -62805,18 +62805,18 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -62839,7 +62839,7 @@
         <v>5</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2.5</v>
@@ -62967,18 +62967,18 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -63001,7 +63001,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
         <v>2.5</v>
@@ -63129,7 +63129,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -63183,7 +63183,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -66232,30 +66232,30 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H40" s="8" t="n">
         <v>0</v>
       </c>
@@ -66266,7 +66266,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -66286,18 +66286,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -66311,16 +66311,16 @@
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -66329,7 +66329,7 @@
         <v>1.0135</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -66340,7 +66340,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -66356,7 +66356,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -66448,14 +66448,14 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -66464,7 +66464,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -66473,16 +66473,16 @@
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0.8333</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>1.5528</v>
@@ -66491,7 +66491,7 @@
         <v>1.0135</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="45">
@@ -66772,28 +66772,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
@@ -66826,18 +66826,18 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -66847,7 +66847,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -66880,18 +66880,18 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -66901,7 +66901,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
@@ -67258,14 +67258,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -67274,12 +67274,12 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -67366,14 +67366,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -67382,12 +67382,12 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -68284,14 +68284,14 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -68300,7 +68300,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -68318,7 +68318,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L78" s="9" t="n">
         <v>2.5</v>
@@ -68392,14 +68392,14 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
@@ -68408,7 +68408,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -68426,7 +68426,7 @@
         <v>5</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>2.5</v>
@@ -68446,7 +68446,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -68554,7 +68554,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -68565,7 +68565,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -68662,7 +68662,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -68673,7 +68673,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -68716,7 +68716,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>N. PRIEDE</t>
+          <t>T. EKE BENITEZ</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -68770,7 +68770,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>T. EKE BENITEZ</t>
+          <t>N. PRIEDE</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -68986,7 +68986,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -69094,7 +69094,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -69148,7 +69148,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>K. BROWN</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -69179,7 +69179,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="10" t="n">
         <v>0</v>
@@ -69188,7 +69188,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N94" s="10" t="n">
         <v>0</v>
@@ -69202,7 +69202,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -69233,7 +69233,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K95" s="10" t="n">
         <v>0</v>
@@ -69242,7 +69242,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N95" s="10" t="n">
         <v>0</v>
@@ -69256,7 +69256,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>E. JOHANSSON</t>
+          <t>I. SANTIBAÑEZ HERRERO</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -69287,7 +69287,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K96" s="10" t="n">
         <v>0</v>
@@ -69296,7 +69296,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N96" s="10" t="n">
         <v>0</v>
@@ -69310,7 +69310,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>E. JOHANSSON</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -69341,7 +69341,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>0</v>
@@ -69350,7 +69350,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N97" s="10" t="n">
         <v>0</v>
@@ -69364,7 +69364,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>I. SANTIBAÑEZ HERRERO</t>
+          <t>K. BROWN</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -60861,14 +60861,14 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
@@ -60877,14 +60877,14 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H39" s="8" t="n">
         <v>0</v>
       </c>
@@ -60895,7 +60895,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>1.5528</v>
@@ -60915,7 +60915,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -60931,7 +60931,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -61023,14 +61023,14 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -61039,12 +61039,12 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -61057,7 +61057,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -61077,7 +61077,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -61093,7 +61093,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -61725,18 +61725,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -61746,7 +61746,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -61833,28 +61833,28 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -61887,14 +61887,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -61903,12 +61903,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -61941,14 +61941,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -61995,7 +61995,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -62011,7 +62011,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -62265,7 +62265,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -62751,18 +62751,18 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -62785,7 +62785,7 @@
         <v>5</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>2.5</v>
@@ -62805,14 +62805,14 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -62839,7 +62839,7 @@
         <v>5</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2.5</v>
@@ -62859,14 +62859,14 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -62893,7 +62893,7 @@
         <v>5</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>2.5</v>
@@ -62913,18 +62913,18 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -62947,7 +62947,7 @@
         <v>5</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>2.5</v>
@@ -63075,7 +63075,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -63086,7 +63086,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -63129,7 +63129,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -63140,7 +63140,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -63237,7 +63237,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -63291,7 +63291,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -65800,23 +65800,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -65834,7 +65834,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.484</v>
@@ -65854,23 +65854,23 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -65888,7 +65888,7 @@
         <v>5</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.484</v>
@@ -66286,14 +66286,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -66302,14 +66302,14 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
@@ -66320,7 +66320,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -66340,28 +66340,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -66374,7 +66374,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -66394,23 +66394,23 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>J. CAMILION CUCCARO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -66428,7 +66428,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.8333</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>1.5528</v>
@@ -66448,7 +66448,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>J. CAMILION CUCCARO</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -66464,7 +66464,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -66772,18 +66772,18 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -66793,7 +66793,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
@@ -66826,18 +66826,18 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -66847,7 +66847,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -67312,14 +67312,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -67328,12 +67328,12 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -67366,14 +67366,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -67382,12 +67382,12 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -67636,7 +67636,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -67690,7 +67690,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -68230,7 +68230,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -68284,14 +68284,14 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -68300,7 +68300,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -68318,7 +68318,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L78" s="9" t="n">
         <v>2.5</v>
@@ -68338,14 +68338,14 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
@@ -68354,7 +68354,7 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -68372,7 +68372,7 @@
         <v>5</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
         <v>2.5</v>
@@ -68392,18 +68392,18 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -68426,7 +68426,7 @@
         <v>5</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>2.5</v>
@@ -68446,18 +68446,18 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -68480,7 +68480,7 @@
         <v>5</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="9" t="n">
         <v>2.5</v>
@@ -68554,7 +68554,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -68565,7 +68565,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -68608,7 +68608,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -68662,7 +68662,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -68673,7 +68673,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -68716,7 +68716,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>N. PRIEDE</t>
+          <t>T. EKE BENITEZ</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -68770,7 +68770,7 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>T. EKE BENITEZ</t>
+          <t>N. PRIEDE</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -68986,7 +68986,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -69040,7 +69040,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t xml:space="preserve">U. DIALLO DIENG </t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -69094,7 +69094,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">U. DIALLO DIENG </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -69148,7 +69148,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -69179,7 +69179,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="10" t="n">
         <v>0</v>
@@ -69188,7 +69188,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N94" s="10" t="n">
         <v>0</v>
@@ -69202,7 +69202,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>K. BROWN</t>
+          <t>E. JOHANSSON</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -69233,7 +69233,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="10" t="n">
         <v>0</v>
@@ -69242,7 +69242,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N95" s="10" t="n">
         <v>0</v>
@@ -69256,7 +69256,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>E. JOHANSSON</t>
+          <t>K. BROWN</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -69287,7 +69287,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K96" s="10" t="n">
         <v>0</v>
@@ -69296,7 +69296,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N96" s="10" t="n">
         <v>0</v>
@@ -69310,7 +69310,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>I. SANTIBAÑEZ HERRERO</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -69341,7 +69341,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>0</v>
@@ -69350,7 +69350,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N97" s="10" t="n">
         <v>0</v>
@@ -69364,7 +69364,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>I. SANTIBAÑEZ HERRERO</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -65800,23 +65800,23 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -65834,7 +65834,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.484</v>
@@ -65854,23 +65854,23 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -65888,7 +65888,7 @@
         <v>5</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.484</v>
@@ -66232,18 +66232,18 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>M. CONNER</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -66257,16 +66257,16 @@
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>1.5528</v>
@@ -66275,7 +66275,7 @@
         <v>1.0135</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -66286,14 +66286,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>C. GUERRERO ALCANTARA</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -66302,12 +66302,12 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
@@ -66320,7 +66320,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.5528</v>
@@ -66340,14 +66340,14 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -66356,25 +66356,25 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.5528</v>
@@ -66383,7 +66383,7 @@
         <v>1.0135</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="43">
@@ -66448,30 +66448,30 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>M. CONNER</t>
+          <t>C. GUERRERO ALCANTARA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H44" s="8" t="n">
         <v>0</v>
       </c>
@@ -66482,7 +66482,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0</v>
+        <v>0.8333</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>1.5528</v>
@@ -66826,18 +66826,18 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>A. SANGARE</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -66847,7 +66847,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
@@ -66880,28 +66880,28 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A. SANGARE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
         <v>3.7</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
@@ -67258,7 +67258,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>T. ALARCON OTERO</t>
+          <t>J. HOBBS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -67274,7 +67274,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -67312,14 +67312,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>B. MASSEY</t>
+          <t>T. ALARCON OTERO</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -67366,14 +67366,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>J. HOBBS</t>
+          <t>B. MASSEY</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -67382,12 +67382,12 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -67636,7 +67636,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -67690,7 +67690,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -68230,18 +68230,18 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -68264,7 +68264,7 @@
         <v>5</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>2.5</v>
@@ -68284,14 +68284,14 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
+          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -68300,7 +68300,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -68318,7 +68318,7 @@
         <v>5</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
         <v>2.5</v>
@@ -68392,14 +68392,14 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>M. ERAUNCETAMURGIL AYESTARAN</t>
+          <t xml:space="preserve">L. GONZALEZ DUARTE </t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
@@ -68408,7 +68408,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -68426,7 +68426,7 @@
         <v>5</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>2.5</v>
@@ -68446,18 +68446,18 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t xml:space="preserve">I. ARIZTIMUÑO LOPEZ </t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -68480,7 +68480,7 @@
         <v>5</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
         <v>2.5</v>
@@ -68554,7 +68554,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -68565,7 +68565,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -68608,7 +68608,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -68662,7 +68662,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -68673,7 +68673,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -68986,7 +68986,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -69094,7 +69094,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -69148,7 +69148,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>K. BROWN</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -69179,7 +69179,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K94" s="10" t="n">
         <v>0</v>
@@ -69188,7 +69188,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N94" s="10" t="n">
         <v>0</v>
@@ -69202,7 +69202,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>E. JOHANSSON</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -69233,7 +69233,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K95" s="10" t="n">
         <v>0</v>
@@ -69242,7 +69242,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N95" s="10" t="n">
         <v>0</v>
@@ -69256,7 +69256,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>K. BROWN</t>
+          <t>E. JOHANSSON</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -69287,7 +69287,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="10" t="n">
         <v>0</v>
@@ -69296,7 +69296,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N96" s="10" t="n">
         <v>0</v>
@@ -69310,7 +69310,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>I. SANTIBAÑEZ HERRERO</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -69341,7 +69341,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>0</v>
@@ -69350,7 +69350,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N97" s="10" t="n">
         <v>0</v>
@@ -69364,7 +69364,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>I. SANTIBAÑEZ HERRERO</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -71858,18 +71858,18 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -71879,7 +71879,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
@@ -71912,18 +71912,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -71933,7 +71933,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -74342,7 +74342,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -74990,14 +74990,14 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
@@ -75044,14 +75044,14 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
@@ -75746,7 +75746,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -75800,7 +75800,7 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t xml:space="preserve">U. DIALLO DIENG </t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
@@ -75854,7 +75854,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">U. DIALLO DIENG </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
@@ -76070,7 +76070,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>E. JOHANSSON</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -76124,7 +76124,7 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>E. JOHANSSON</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -76232,7 +76232,7 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>N. BOSCH DURAN</t>
+          <t>Z. HERNANDEZ ORTIZ</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -76286,7 +76286,7 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>H. VAN SCHAIK</t>
+          <t>A. VILARO ARAGONES</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -76340,7 +76340,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>A. VILARO ARAGONES</t>
+          <t>N. BOSCH DURAN</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -76394,7 +76394,7 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Z. HERNANDEZ ORTIZ</t>
+          <t>L. SAKEVICIUTE</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -76448,7 +76448,7 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>L. SAKEVICIUTE</t>
+          <t>H. VAN SCHAIK</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -76502,14 +76502,14 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>E. BALOGUN</t>
+          <t>H. PUEYO MELCHOR</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
@@ -76523,7 +76523,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H124" s="8" t="n">
@@ -76610,7 +76610,7 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>V. TAKACS-KISS</t>
+          <t>C. BIBBY</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -76664,7 +76664,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>H. PUEYO MELCHOR</t>
+          <t>V. TAKACS-KISS</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -76718,14 +76718,14 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>C. BIBBY</t>
+          <t>E. BALOGUN</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H128" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -71858,18 +71858,18 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -71879,7 +71879,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
@@ -71912,18 +71912,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -71933,7 +71933,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -72398,14 +72398,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -72452,14 +72452,14 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -72473,7 +72473,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -73532,14 +73532,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -73548,25 +73548,25 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.5528</v>
@@ -73575,7 +73575,7 @@
         <v>1.0135</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -73586,14 +73586,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -73602,25 +73602,25 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.5528</v>
@@ -73629,7 +73629,7 @@
         <v>1.0135</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="71">
@@ -74342,7 +74342,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -74990,14 +74990,14 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
@@ -75044,14 +75044,14 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
@@ -75314,7 +75314,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -75325,7 +75325,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -75368,7 +75368,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -75422,7 +75422,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -75433,7 +75433,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -75908,7 +75908,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>I. SANTIBAÑEZ HERRERO</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -75962,7 +75962,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>I. SANTIBAÑEZ HERRERO</t>
+          <t>E. JOHANSSON</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -75993,7 +75993,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>0</v>
@@ -76002,7 +76002,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N114" s="10" t="n">
         <v>0</v>
@@ -76016,7 +76016,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>K. BROWN</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -76070,7 +76070,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>E. JOHANSSON</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -76124,7 +76124,7 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>K. BROWN</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -76155,7 +76155,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K117" s="10" t="n">
         <v>0</v>
@@ -76164,7 +76164,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N117" s="10" t="n">
         <v>0</v>
@@ -76232,7 +76232,7 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Z. HERNANDEZ ORTIZ</t>
+          <t>L. SAKEVICIUTE</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -76340,7 +76340,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>N. BOSCH DURAN</t>
+          <t>H. VAN SCHAIK</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -76394,7 +76394,7 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>L. SAKEVICIUTE</t>
+          <t>Z. HERNANDEZ ORTIZ</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -76448,7 +76448,7 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>H. VAN SCHAIK</t>
+          <t>N. BOSCH DURAN</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -76610,14 +76610,14 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>C. BIBBY</t>
+          <t>E. BALOGUN</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
@@ -76631,7 +76631,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
@@ -76664,7 +76664,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>V. TAKACS-KISS</t>
+          <t>C. BIBBY</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -76718,14 +76718,14 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>E. BALOGUN</t>
+          <t>V. TAKACS-KISS</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H128" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -71264,23 +71264,23 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -71289,16 +71289,16 @@
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>1.686</v>
@@ -71307,7 +71307,7 @@
         <v>1.0183</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.1163</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="28">
@@ -71318,23 +71318,23 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -71343,16 +71343,16 @@
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.686</v>
@@ -71361,7 +71361,7 @@
         <v>1.0183</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>0.0581</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="29">
@@ -72398,14 +72398,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>K. FAYE</t>
+          <t>P. ROBINSON</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -72452,14 +72452,14 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>P. ROBINSON</t>
+          <t>K. FAYE</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -72473,7 +72473,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -73532,14 +73532,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -73548,25 +73548,25 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H69" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.5528</v>
@@ -73575,7 +73575,7 @@
         <v>1.0135</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="70">
@@ -73586,14 +73586,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -73602,25 +73602,25 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.5528</v>
@@ -73629,7 +73629,7 @@
         <v>1.0135</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -74342,7 +74342,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -75314,7 +75314,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>M. ORTEGA CAMPOS</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -75368,7 +75368,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -75379,7 +75379,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -75422,7 +75422,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>M. ORTEGA CAMPOS</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -75433,7 +75433,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -75746,7 +75746,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -75854,7 +75854,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
@@ -75908,7 +75908,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>I. SANTIBAÑEZ HERRERO</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -76016,7 +76016,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -76047,7 +76047,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K115" s="10" t="n">
         <v>0</v>
@@ -76056,7 +76056,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N115" s="10" t="n">
         <v>0</v>
@@ -76070,7 +76070,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>I. SANTIBAÑEZ HERRERO</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -76101,7 +76101,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K116" s="10" t="n">
         <v>0</v>
@@ -76110,7 +76110,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N116" s="10" t="n">
         <v>0</v>
@@ -76340,7 +76340,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>H. VAN SCHAIK</t>
+          <t>Z. HERNANDEZ ORTIZ</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -76394,7 +76394,7 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Z. HERNANDEZ ORTIZ</t>
+          <t>H. VAN SCHAIK</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -76502,7 +76502,7 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>H. PUEYO MELCHOR</t>
+          <t>C. BIBBY</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
@@ -76556,14 +76556,14 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>I. HERNANDEZ LOPEZ</t>
+          <t>E. BALOGUN</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
@@ -76577,7 +76577,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
@@ -76610,14 +76610,14 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>E. BALOGUN</t>
+          <t>V. TAKACS-KISS</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
@@ -76631,7 +76631,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
@@ -76664,7 +76664,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>C. BIBBY</t>
+          <t>I. HERNANDEZ LOPEZ</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -76718,7 +76718,7 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>V. TAKACS-KISS</t>
+          <t>H. PUEYO MELCHOR</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">

--- a/fulls/full_mestre_lf_2026.xlsx
+++ b/fulls/full_mestre_lf_2026.xlsx
@@ -71264,23 +71264,23 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>M. DOOGAN</t>
+          <t>S. SHAW</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -71289,16 +71289,16 @@
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>1.686</v>
@@ -71307,7 +71307,7 @@
         <v>1.0183</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>0.0581</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="28">
@@ -71318,23 +71318,23 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>S. SHAW</t>
+          <t>M. DOOGAN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -71343,16 +71343,16 @@
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.686</v>
@@ -71361,7 +71361,7 @@
         <v>1.0183</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>0.1163</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="29">
@@ -71858,18 +71858,18 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>R. IGBOWKE</t>
+          <t>R. AGUILAR MOTTA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -71879,7 +71879,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
@@ -71912,18 +71912,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>R. AGUILAR MOTTA</t>
+          <t>R. IGBOWKE</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -71933,7 +71933,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
@@ -73532,14 +73532,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>A. BULGAK</t>
+          <t>I. MARTIN CARRION</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -73548,25 +73548,25 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.5528</v>
@@ -73575,7 +73575,7 @@
         <v>1.0135</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>0.1553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -73586,14 +73586,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>I. MARTIN CARRION</t>
+          <t>A. BULGAK</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -73602,25 +73602,25 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.5528</v>
@@ -73629,7 +73629,7 @@
         <v>1.0135</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>0</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="71">
@@ -74342,7 +74342,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>K. COOPER</t>
+          <t>J. FEQUIERE</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>J. FEQUIERE</t>
+          <t>K. COOPER</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -74990,14 +74990,14 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>L. HOWARD</t>
+          <t>M. GRETTER</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
@@ -75044,14 +75044,14 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>M. GRETTER</t>
+          <t>L. HOWARD</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
@@ -75314,7 +75314,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>C. MUHATE PEÑA</t>
+          <t>T. MOORE</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -75325,7 +75325,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -75368,7 +75368,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>T. MOORE</t>
+          <t>C. MUHATE PEÑA</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -75379,7 +75379,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -75746,7 +75746,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ ARRIBAS</t>
+          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -75854,7 +75854,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. GERVASINI LACORZANA </t>
+          <t>L. RODRIGUEZ ARRIBAS</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
@@ -75908,7 +75908,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>S. ROUMY</t>
+          <t>C. SORIANO PEREZ</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -75939,7 +75939,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>0</v>
@@ -75948,7 +75948,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N113" s="10" t="n">
         <v>0</v>
@@ -76016,7 +76016,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>C. SORIANO PEREZ</t>
+          <t>S. ROUMY</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -76047,7 +76047,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K115" s="10" t="n">
         <v>0</v>
@@ -76056,7 +76056,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N115" s="10" t="n">
         <v>0</v>
@@ -76232,7 +76232,7 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>L. SAKEVICIUTE</t>
+          <t>H. VAN SCHAIK</t>
         </is>
       </c>
       <c r="C119" s="8" t="n">
@@ -76286,7 +76286,7 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>A. VILARO ARAGONES</t>
+          <t>L. SAKEVICIUTE</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -76340,7 +76340,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Z. HERNANDEZ ORTIZ</t>
+          <t>A. VILARO ARAGONES</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -76394,7 +76394,7 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>H. VAN SCHAIK</t>
+          <t>Z. HERNANDEZ ORTIZ</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -76610,7 +76610,7 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>V. TAKACS-KISS</t>
+          <t>I. HERNANDEZ LOPEZ</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -76664,7 +76664,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>I. HERNANDEZ LOPEZ</t>
+          <t>H. PUEYO MELCHOR</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -76718,7 +76718,7 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>H. PUEYO MELCHOR</t>
+          <t>V. TAKACS-KISS</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
